--- a/Collections/EURO/Austria/#EURO#Austria#Commemorative#[2005-present]#UNC.xlsx
+++ b/Collections/EURO/Austria/#EURO#Austria#Commemorative#[2005-present]#UNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Austria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0056F4-59D0-42EF-8D6B-5EC7B61B9E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE39009-5622-4E07-9AFA-9648A58D90F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1324,7 +1327,7 @@
         <v>29</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F20" s="9">
         <v>2590000</v>

--- a/Collections/EURO/Austria/#EURO#Austria#Commemorative#[2005-present]#UNC.xlsx
+++ b/Collections/EURO/Austria/#EURO#Austria#Commemorative#[2005-present]#UNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Austria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE39009-5622-4E07-9AFA-9648A58D90F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA75E11-2B56-4147-BC02-63C5C9DEB59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="40">
   <si>
     <t>AT</t>
   </si>
@@ -805,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="13" customWidth="1"/>
@@ -1390,7 +1390,34 @@
         <v>5</v>
       </c>
       <c r="H22" s="11" t="str">
-        <f t="shared" ref="H22" si="3">IF(OR(AND(G22&gt;1,G22&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="H22:H23" si="3">IF(OR(AND(G22&gt;1,G22&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="11" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -1434,12 +1461,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G21">
+  <conditionalFormatting sqref="G21 G23">
     <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G21">
+  <conditionalFormatting sqref="G21 G23">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
